--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-03-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>רובין Sexistential</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%a9%d7%97%d7%95%d7%a8-%d7%96%d7%95%d7%94%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99%d7%9f-sexistential/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שחור זוהר" של הילה רוח הוא יצירה בת 15 שירים שמנסה להלך על קו עדין בין פופ נגיש לבין אמירה כמעט אוונגרדית.  זה לא אלבום שמבקש לרצות אלא  להטרי, לעורר, ולפעמים גם לבלבל. הסינגלים "טבע" ו־"זאת השנה" מתפקדים כשער כניסה</v>
+        <v>בקריירה שנמשכת כבר שני עשורים, רובין (Robyn), הזמרת השוודית, יצרה כמה מהלהיטים הבולטים בפופ – ובראשם “Dancing On My Own”, המנון נצחי ואיקוני על מציאת הדרך האישית מתוך שברון לב. אך באלבומה התשיעי “Sexistential”, אנו פוגשים אותה חסרת עוגן ותוהה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>רובין Sexistential</v>
       </c>
     </row>
   </sheetData>
